--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/141.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/141.xlsx
@@ -426,13 +426,13 @@
         <v>-6.794440688476174</v>
       </c>
       <c r="E2">
-        <v>-9.92529856844113</v>
+        <v>-7.719161886124363</v>
       </c>
       <c r="F2">
-        <v>1.74457390937696</v>
+        <v>1.834673775044657</v>
       </c>
       <c r="G2">
-        <v>-5.679533351295511</v>
+        <v>-3.5441222304628</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.337621527440103</v>
       </c>
       <c r="E3">
-        <v>-8.018829125107942</v>
+        <v>-8.907727816547563</v>
       </c>
       <c r="F3">
-        <v>1.341758722213228</v>
+        <v>2.006044766601013</v>
       </c>
       <c r="G3">
-        <v>-5.197928428424496</v>
+        <v>-2.635857509036053</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.942207956698543</v>
       </c>
       <c r="E4">
-        <v>-8.798876886825191</v>
+        <v>-8.383959984346403</v>
       </c>
       <c r="F4">
-        <v>1.443697614801735</v>
+        <v>1.611866137978868</v>
       </c>
       <c r="G4">
-        <v>-4.597835770157426</v>
+        <v>-2.695281801465971</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.660934504094871</v>
       </c>
       <c r="E5">
-        <v>-10.7245470599509</v>
+        <v>-9.723917329320031</v>
       </c>
       <c r="F5">
-        <v>1.095158716604232</v>
+        <v>2.310380323450329</v>
       </c>
       <c r="G5">
-        <v>-3.553908203076885</v>
+        <v>-2.97159979544678</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.495296685331458</v>
       </c>
       <c r="E6">
-        <v>-11.07752349495278</v>
+        <v>-10.10128865380122</v>
       </c>
       <c r="F6">
-        <v>1.920214306527345</v>
+        <v>1.910762634461403</v>
       </c>
       <c r="G6">
-        <v>-4.764736923519783</v>
+        <v>-3.337815653546498</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.458637166084893</v>
       </c>
       <c r="E7">
-        <v>-10.3432721908751</v>
+        <v>-9.199945715788523</v>
       </c>
       <c r="F7">
-        <v>2.02856476281352</v>
+        <v>2.297366671552349</v>
       </c>
       <c r="G7">
-        <v>-3.749485301900409</v>
+        <v>-2.643508179777309</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.544969236362538</v>
       </c>
       <c r="E8">
-        <v>-11.82759275873925</v>
+        <v>-11.42755189337566</v>
       </c>
       <c r="F8">
-        <v>2.224947479730005</v>
+        <v>2.547571732098328</v>
       </c>
       <c r="G8">
-        <v>-3.84950350373287</v>
+        <v>-2.65667752993253</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.743539956784317</v>
       </c>
       <c r="E9">
-        <v>-12.54132554708817</v>
+        <v>-11.51990559228809</v>
       </c>
       <c r="F9">
-        <v>2.078704184970169</v>
+        <v>2.595540831659642</v>
       </c>
       <c r="G9">
-        <v>-2.395283475242755</v>
+        <v>-2.118790022348365</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.03141177592092</v>
       </c>
       <c r="E10">
-        <v>-11.97137633695679</v>
+        <v>-14.01120481134186</v>
       </c>
       <c r="F10">
-        <v>2.260824071945251</v>
+        <v>2.335728365975994</v>
       </c>
       <c r="G10">
-        <v>-2.690746354077169</v>
+        <v>-2.55965206126757</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.385405532887674</v>
       </c>
       <c r="E11">
-        <v>-14.64908566006231</v>
+        <v>-13.04066679049196</v>
       </c>
       <c r="F11">
-        <v>2.736495828920006</v>
+        <v>2.718546764036146</v>
       </c>
       <c r="G11">
-        <v>-3.717700754177867</v>
+        <v>-1.495702314765517</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.773726244255662</v>
       </c>
       <c r="E12">
-        <v>-15.43042403687175</v>
+        <v>-14.47931769798876</v>
       </c>
       <c r="F12">
-        <v>2.923117064361901</v>
+        <v>2.644480777817037</v>
       </c>
       <c r="G12">
-        <v>-2.651347551614303</v>
+        <v>-1.260911804029326</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.162667843644819</v>
       </c>
       <c r="E13">
-        <v>-15.86298387408442</v>
+        <v>-14.51335370863041</v>
       </c>
       <c r="F13">
-        <v>2.8606233707599</v>
+        <v>3.502502076901959</v>
       </c>
       <c r="G13">
-        <v>-2.263454241323437</v>
+        <v>-0.9267718216596064</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.523316078978831</v>
       </c>
       <c r="E14">
-        <v>-17.60302284068771</v>
+        <v>-15.84777725836666</v>
       </c>
       <c r="F14">
-        <v>2.51375114777683</v>
+        <v>3.758812205206571</v>
       </c>
       <c r="G14">
-        <v>-1.719531609221181</v>
+        <v>-1.074912113450913</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.835054252976311</v>
       </c>
       <c r="E15">
-        <v>-16.96643260705945</v>
+        <v>-16.91398382110261</v>
       </c>
       <c r="F15">
-        <v>2.72100370175285</v>
+        <v>3.356661368699884</v>
       </c>
       <c r="G15">
-        <v>-1.589364269162577</v>
+        <v>-0.1010092056170371</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.081737916357058</v>
       </c>
       <c r="E16">
-        <v>-17.39217709089058</v>
+        <v>-17.21344727875584</v>
       </c>
       <c r="F16">
-        <v>3.067069094885593</v>
+        <v>3.919858425454434</v>
       </c>
       <c r="G16">
-        <v>-2.21202160582532</v>
+        <v>-0.125520484789801</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.251907591815044</v>
       </c>
       <c r="E17">
-        <v>-19.49192180487114</v>
+        <v>-16.55982092591073</v>
       </c>
       <c r="F17">
-        <v>2.386315106530154</v>
+        <v>4.308284870831539</v>
       </c>
       <c r="G17">
-        <v>-0.7172142890237402</v>
+        <v>0.5716539214163968</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.34088796885514</v>
       </c>
       <c r="E18">
-        <v>-18.58460128116831</v>
+        <v>-18.83937775731385</v>
       </c>
       <c r="F18">
-        <v>3.91349822053574</v>
+        <v>4.178092022868347</v>
       </c>
       <c r="G18">
-        <v>-0.4614978199338159</v>
+        <v>0.7439347112800694</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.350583155757276</v>
       </c>
       <c r="E19">
-        <v>-19.24695853190022</v>
+        <v>-18.90000043885454</v>
       </c>
       <c r="F19">
-        <v>3.842851734955386</v>
+        <v>4.175931640681845</v>
       </c>
       <c r="G19">
-        <v>0.2110957856432933</v>
+        <v>1.097788992336149</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.285537378405875</v>
       </c>
       <c r="E20">
-        <v>-21.58016872334622</v>
+        <v>-20.12329976491657</v>
       </c>
       <c r="F20">
-        <v>4.274565347333183</v>
+        <v>4.735480567394466</v>
       </c>
       <c r="G20">
-        <v>0.4929092852192924</v>
+        <v>1.425185393442373</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.149847692565768</v>
       </c>
       <c r="E21">
-        <v>-20.95058856748184</v>
+        <v>-21.37701232241411</v>
       </c>
       <c r="F21">
-        <v>4.211097493665489</v>
+        <v>4.672191641085779</v>
       </c>
       <c r="G21">
-        <v>1.072562635326902</v>
+        <v>1.595784426172096</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.951289039643137</v>
       </c>
       <c r="E22">
-        <v>-21.45395562427844</v>
+        <v>-20.66234666841961</v>
       </c>
       <c r="F22">
-        <v>4.42035635349109</v>
+        <v>4.555053863390707</v>
       </c>
       <c r="G22">
-        <v>2.214737262376394</v>
+        <v>2.656407074407181</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.700109850370958</v>
       </c>
       <c r="E23">
-        <v>-22.2550834325014</v>
+        <v>-21.81295040123651</v>
       </c>
       <c r="F23">
-        <v>4.65347053778251</v>
+        <v>4.952989966551949</v>
       </c>
       <c r="G23">
-        <v>1.436881550832618</v>
+        <v>2.338727124458718</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.406978985707958</v>
       </c>
       <c r="E24">
-        <v>-24.81620266380544</v>
+        <v>-22.36620312770161</v>
       </c>
       <c r="F24">
-        <v>4.676939843038626</v>
+        <v>5.129520030292941</v>
       </c>
       <c r="G24">
-        <v>1.006030601624169</v>
+        <v>2.823533344866208</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.080885599121382</v>
       </c>
       <c r="E25">
-        <v>-25.2857737190828</v>
+        <v>-23.88937800255157</v>
       </c>
       <c r="F25">
-        <v>4.607646909794447</v>
+        <v>5.472154325643289</v>
       </c>
       <c r="G25">
-        <v>2.155584434680696</v>
+        <v>2.379254822950475</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.731928292570305</v>
       </c>
       <c r="E26">
-        <v>-24.92389883265585</v>
+        <v>-23.62088930711081</v>
       </c>
       <c r="F26">
-        <v>4.240004202553581</v>
+        <v>5.127949445697233</v>
       </c>
       <c r="G26">
-        <v>3.308634203826694</v>
+        <v>3.76825048322587</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.372228389981417</v>
       </c>
       <c r="E27">
-        <v>-23.84343663374376</v>
+        <v>-23.52379882438635</v>
       </c>
       <c r="F27">
-        <v>5.119120705918196</v>
+        <v>5.304279044526747</v>
       </c>
       <c r="G27">
-        <v>2.062918954490956</v>
+        <v>3.18918641022425</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.012837685337343</v>
       </c>
       <c r="E28">
-        <v>-26.29404751383862</v>
+        <v>-23.77742506813395</v>
       </c>
       <c r="F28">
-        <v>4.971606695562466</v>
+        <v>4.868590925350319</v>
       </c>
       <c r="G28">
-        <v>1.44727666382593</v>
+        <v>3.021047112830205</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.662038701537713</v>
       </c>
       <c r="E29">
-        <v>-24.74040053739104</v>
+        <v>-23.19475084604101</v>
       </c>
       <c r="F29">
-        <v>4.394804532584336</v>
+        <v>5.313457355349765</v>
       </c>
       <c r="G29">
-        <v>3.230604645466072</v>
+        <v>2.711537589272664</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.326560292591733</v>
       </c>
       <c r="E30">
-        <v>-24.33699501583975</v>
+        <v>-23.98875083617589</v>
       </c>
       <c r="F30">
-        <v>4.165823901632885</v>
+        <v>5.25654851477744</v>
       </c>
       <c r="G30">
-        <v>2.573368660645642</v>
+        <v>2.34316656602688</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.016732989830489</v>
       </c>
       <c r="E31">
-        <v>-23.97795948261562</v>
+        <v>-23.22911290681121</v>
       </c>
       <c r="F31">
-        <v>4.773683215276774</v>
+        <v>4.942501178497702</v>
       </c>
       <c r="G31">
-        <v>1.447174036914212</v>
+        <v>2.089234480982623</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.740835711114955</v>
       </c>
       <c r="E32">
-        <v>-22.89601647270301</v>
+        <v>-24.14395975431479</v>
       </c>
       <c r="F32">
-        <v>4.823226212903407</v>
+        <v>5.144255029653938</v>
       </c>
       <c r="G32">
-        <v>1.136744181696753</v>
+        <v>2.501854255906305</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.505524934253845</v>
       </c>
       <c r="E33">
-        <v>-22.84274803295079</v>
+        <v>-23.42734232802298</v>
       </c>
       <c r="F33">
-        <v>4.616768891634075</v>
+        <v>5.282855806755546</v>
       </c>
       <c r="G33">
-        <v>2.069500319023028</v>
+        <v>1.88411307936938</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.314088942731083</v>
       </c>
       <c r="E34">
-        <v>-24.46064047014518</v>
+        <v>-22.32146180450583</v>
       </c>
       <c r="F34">
-        <v>4.38270042809463</v>
+        <v>4.74216880580467</v>
       </c>
       <c r="G34">
-        <v>1.586819468851749</v>
+        <v>2.224453713534155</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.173806347813101</v>
       </c>
       <c r="E35">
-        <v>-23.43871785473025</v>
+        <v>-22.65556355984373</v>
       </c>
       <c r="F35">
-        <v>4.763495952957146</v>
+        <v>5.21694261251479</v>
       </c>
       <c r="G35">
-        <v>-0.706431842202334</v>
+        <v>1.485304900435538</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.089265117424795</v>
       </c>
       <c r="E36">
-        <v>-24.16831841600205</v>
+        <v>-22.16770199804939</v>
       </c>
       <c r="F36">
-        <v>4.49880771674062</v>
+        <v>5.533897518378353</v>
       </c>
       <c r="G36">
-        <v>0.887307817494826</v>
+        <v>1.493779897016072</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.061156265584754</v>
       </c>
       <c r="E37">
-        <v>-23.49958054539334</v>
+        <v>-22.05879672663892</v>
       </c>
       <c r="F37">
-        <v>4.853556056989508</v>
+        <v>5.093211030293433</v>
       </c>
       <c r="G37">
-        <v>0.5635033582987112</v>
+        <v>1.448302932943104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.085450033311868</v>
       </c>
       <c r="E38">
-        <v>-22.45033311781611</v>
+        <v>-21.27254042705716</v>
       </c>
       <c r="F38">
-        <v>4.958556595498762</v>
+        <v>5.408643396870651</v>
       </c>
       <c r="G38">
-        <v>0.9009472651166233</v>
+        <v>2.073598774400645</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.157718230650969</v>
       </c>
       <c r="E39">
-        <v>-21.57674972547043</v>
+        <v>-20.84830845354459</v>
       </c>
       <c r="F39">
-        <v>4.62376859618773</v>
+        <v>5.545741515503581</v>
       </c>
       <c r="G39">
-        <v>1.070248563994952</v>
+        <v>2.448296250171976</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.271541049873317</v>
       </c>
       <c r="E40">
-        <v>-20.81154177307632</v>
+        <v>-20.65438561111413</v>
       </c>
       <c r="F40">
-        <v>4.219314898301261</v>
+        <v>5.387215188895033</v>
       </c>
       <c r="G40">
-        <v>1.356094308037783</v>
+        <v>1.598244161507774</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.418808136665453</v>
       </c>
       <c r="E41">
-        <v>-20.94475136448595</v>
+        <v>-19.74231471817725</v>
       </c>
       <c r="F41">
-        <v>4.452654398526242</v>
+        <v>5.36036448790069</v>
       </c>
       <c r="G41">
-        <v>0.5221811288775282</v>
+        <v>1.245005641921999</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.588574518423585</v>
       </c>
       <c r="E42">
-        <v>-21.58379150255236</v>
+        <v>-20.08599872451539</v>
       </c>
       <c r="F42">
-        <v>4.347300975503396</v>
+        <v>5.431396992690748</v>
       </c>
       <c r="G42">
-        <v>0.1969597561906054</v>
+        <v>1.077833023825422</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.770598105744939</v>
       </c>
       <c r="E43">
-        <v>-17.91721289581389</v>
+        <v>-18.59795575101693</v>
       </c>
       <c r="F43">
-        <v>4.855178000364189</v>
+        <v>5.434867852108478</v>
       </c>
       <c r="G43">
-        <v>0.510580977307922</v>
+        <v>1.634229791519652</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.955883262309582</v>
       </c>
       <c r="E44">
-        <v>-19.19725400119203</v>
+        <v>-18.53566206256742</v>
       </c>
       <c r="F44">
-        <v>5.273092668546151</v>
+        <v>5.378475912795499</v>
       </c>
       <c r="G44">
-        <v>1.064415382754756</v>
+        <v>1.287092607362754</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.13892481762295</v>
       </c>
       <c r="E45">
-        <v>-18.67354051067896</v>
+        <v>-18.10543438946869</v>
       </c>
       <c r="F45">
-        <v>4.615105529889253</v>
+        <v>5.83057564695619</v>
       </c>
       <c r="G45">
-        <v>1.628386678642838</v>
+        <v>2.098119985210027</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.313708258478642</v>
       </c>
       <c r="E46">
-        <v>-16.5900303760159</v>
+        <v>-16.78322866260514</v>
       </c>
       <c r="F46">
-        <v>4.749037628308683</v>
+        <v>5.588092627339108</v>
       </c>
       <c r="G46">
-        <v>-0.1465556911463301</v>
+        <v>1.885543235042346</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.475398060223227</v>
       </c>
       <c r="E47">
-        <v>-15.84741498044605</v>
+        <v>-18.30137693130659</v>
       </c>
       <c r="F47">
-        <v>4.590193208617461</v>
+        <v>5.344845852976644</v>
       </c>
       <c r="G47">
-        <v>0.2926643171853961</v>
+        <v>1.682504166573304</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.620486127745089</v>
       </c>
       <c r="E48">
-        <v>-15.94082381380226</v>
+        <v>-16.30420668207377</v>
       </c>
       <c r="F48">
-        <v>4.983667724947226</v>
+        <v>5.483401898238501</v>
       </c>
       <c r="G48">
-        <v>1.077157672535411</v>
+        <v>1.610873892740094</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.750333663875061</v>
       </c>
       <c r="E49">
-        <v>-17.41566628556836</v>
+        <v>-16.3807378928034</v>
       </c>
       <c r="F49">
-        <v>4.500520780529609</v>
+        <v>5.49818162943925</v>
       </c>
       <c r="G49">
-        <v>1.915828105635598</v>
+        <v>1.924303102216133</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.865440211482763</v>
       </c>
       <c r="E50">
-        <v>-16.4491676635333</v>
+        <v>-16.03680934886885</v>
       </c>
       <c r="F50">
-        <v>5.017496592942752</v>
+        <v>5.670245136144346</v>
       </c>
       <c r="G50">
-        <v>0.4001047621169032</v>
+        <v>2.332407293024249</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.965917611849534</v>
       </c>
       <c r="E51">
-        <v>-17.33246916109944</v>
+        <v>-15.7239370796789</v>
       </c>
       <c r="F51">
-        <v>4.344351987549429</v>
+        <v>5.183049131861845</v>
       </c>
       <c r="G51">
-        <v>0.1860945457307173</v>
+        <v>1.541143872046425</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.052216794744735</v>
       </c>
       <c r="E52">
-        <v>-14.6092849020089</v>
+        <v>-14.60657687455231</v>
       </c>
       <c r="F52">
-        <v>4.538643905141248</v>
+        <v>5.576904697196897</v>
       </c>
       <c r="G52">
-        <v>0.5321260076774988</v>
+        <v>2.406563513103924</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.129668648912336</v>
       </c>
       <c r="E53">
-        <v>-11.44649902862375</v>
+        <v>-13.35783205304118</v>
       </c>
       <c r="F53">
-        <v>5.137069770802055</v>
+        <v>5.471481691312216</v>
       </c>
       <c r="G53">
-        <v>1.059270794986729</v>
+        <v>1.151585357349306</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.201513567434401</v>
       </c>
       <c r="E54">
-        <v>-14.12880022437305</v>
+        <v>-14.19174148460566</v>
       </c>
       <c r="F54">
-        <v>4.961926394093351</v>
+        <v>5.814960921413419</v>
       </c>
       <c r="G54">
-        <v>0.4785977968530231</v>
+        <v>1.22401678320302</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.268999803401638</v>
       </c>
       <c r="E55">
-        <v>-12.75802661377722</v>
+        <v>-12.78243508867857</v>
       </c>
       <c r="F55">
-        <v>4.807328185708879</v>
+        <v>5.721149969781181</v>
       </c>
       <c r="G55">
-        <v>0.277257038245628</v>
+        <v>2.053467346976337</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.334375250607329</v>
       </c>
       <c r="E56">
-        <v>-12.07497423683026</v>
+        <v>-13.08151362604115</v>
       </c>
       <c r="F56">
-        <v>4.678160856590352</v>
+        <v>5.455288765322291</v>
       </c>
       <c r="G56">
-        <v>-0.471863138017274</v>
+        <v>0.4420725479182441</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.402998580840783</v>
       </c>
       <c r="E57">
-        <v>-12.0367358023095</v>
+        <v>-11.14492983055695</v>
       </c>
       <c r="F57">
-        <v>4.595456655094849</v>
+        <v>5.836425577554761</v>
       </c>
       <c r="G57">
-        <v>-0.3794658120162152</v>
+        <v>0.7811220693227027</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.478493414662702</v>
       </c>
       <c r="E58">
-        <v>-12.52218821593176</v>
+        <v>-11.42105353317465</v>
       </c>
       <c r="F58">
-        <v>4.968732260674751</v>
+        <v>5.371118353523833</v>
       </c>
       <c r="G58">
-        <v>0.7409519097491861</v>
+        <v>1.050663376584623</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.561534554750106</v>
       </c>
       <c r="E59">
-        <v>-12.66586763924712</v>
+        <v>-10.53050647719624</v>
       </c>
       <c r="F59">
-        <v>4.376674883606666</v>
+        <v>5.617335653392736</v>
       </c>
       <c r="G59">
-        <v>0.08794018103686591</v>
+        <v>0.5973603075288376</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.652863237181603</v>
       </c>
       <c r="E60">
-        <v>-11.44007312400687</v>
+        <v>-11.92220616618151</v>
       </c>
       <c r="F60">
-        <v>4.785981157738735</v>
+        <v>5.715068096309827</v>
       </c>
       <c r="G60">
-        <v>0.05869482174294424</v>
+        <v>1.436202888997067</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.754328110618445</v>
       </c>
       <c r="E61">
-        <v>-11.29079650681802</v>
+        <v>-10.8014133777571</v>
       </c>
       <c r="F61">
-        <v>4.42342793982067</v>
+        <v>5.860956849821265</v>
       </c>
       <c r="G61">
-        <v>-0.1195846766378877</v>
+        <v>1.142795858942541</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.868041989348894</v>
       </c>
       <c r="E62">
-        <v>-11.10943112281082</v>
+        <v>-10.78581731327468</v>
       </c>
       <c r="F62">
-        <v>4.32760736886924</v>
+        <v>5.866980737574423</v>
       </c>
       <c r="G62">
-        <v>-1.489978381528117</v>
+        <v>1.023616219528778</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.992557469721188</v>
       </c>
       <c r="E63">
-        <v>-11.85356355717324</v>
+        <v>-10.22739306949282</v>
       </c>
       <c r="F63">
-        <v>4.725084556489333</v>
+        <v>5.398949841523091</v>
       </c>
       <c r="G63">
-        <v>-0.7754765799693738</v>
+        <v>0.4888869723890779</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.125528593269785</v>
       </c>
       <c r="E64">
-        <v>-10.09278417961482</v>
+        <v>-9.605860011940065</v>
       </c>
       <c r="F64">
-        <v>5.056754580896227</v>
+        <v>5.824629625738895</v>
       </c>
       <c r="G64">
-        <v>-1.005407209853915</v>
+        <v>0.9106306108189915</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.26392346762477</v>
       </c>
       <c r="E65">
-        <v>-10.06969349064971</v>
+        <v>-10.59089820656253</v>
       </c>
       <c r="F65">
-        <v>4.893161959252158</v>
+        <v>5.49154474980802</v>
       </c>
       <c r="G65">
-        <v>-0.5906984806949526</v>
+        <v>0.4718509050439884</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.406059913145717</v>
       </c>
       <c r="E66">
-        <v>-10.0029166129326</v>
+        <v>-11.26423247828903</v>
       </c>
       <c r="F66">
-        <v>4.902287254561397</v>
+        <v>5.73840320604669</v>
       </c>
       <c r="G66">
-        <v>-0.9291686566300387</v>
+        <v>1.02256015550175</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.546391947483694</v>
       </c>
       <c r="E67">
-        <v>-7.967077724148284</v>
+        <v>-9.260831048821652</v>
       </c>
       <c r="F67">
-        <v>4.883216580214147</v>
+        <v>5.608669273624647</v>
       </c>
       <c r="G67">
-        <v>-0.5973493666833484</v>
+        <v>-0.1202732701100561</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.678575075777916</v>
       </c>
       <c r="E68">
-        <v>-8.623769853896594</v>
+        <v>-10.09731265362249</v>
       </c>
       <c r="F68">
-        <v>4.929186000865103</v>
+        <v>5.446860955366209</v>
       </c>
       <c r="G68">
-        <v>-1.901542092424772</v>
+        <v>1.054894253783812</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.796754323759893</v>
       </c>
       <c r="E69">
-        <v>-7.826699558384511</v>
+        <v>-10.57681465239867</v>
       </c>
       <c r="F69">
-        <v>5.126915643178539</v>
+        <v>5.244911609502912</v>
       </c>
       <c r="G69">
-        <v>-1.348975625919479</v>
+        <v>0.1042280650900801</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.898470349359163</v>
       </c>
       <c r="E70">
-        <v>-9.515100335878335</v>
+        <v>-9.173137149663114</v>
       </c>
       <c r="F70">
-        <v>4.750977664766039</v>
+        <v>5.424554677943624</v>
       </c>
       <c r="G70">
-        <v>-1.375552685508748</v>
+        <v>0.75828592619281</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.977981935478672</v>
       </c>
       <c r="E71">
-        <v>-8.800787902856428</v>
+        <v>-8.477183150268305</v>
       </c>
       <c r="F71">
-        <v>4.663755547455668</v>
+        <v>5.094113950762484</v>
       </c>
       <c r="G71">
-        <v>-0.9791876891828871</v>
+        <v>-0.3022969954958038</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.027874392807471</v>
       </c>
       <c r="E72">
-        <v>-9.905436681443488</v>
+        <v>-9.242413745032456</v>
       </c>
       <c r="F72">
-        <v>4.64492509965523</v>
+        <v>5.263930925071189</v>
       </c>
       <c r="G72">
-        <v>-1.039078768533842</v>
+        <v>-0.7796511778943949</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.043885269988843</v>
       </c>
       <c r="E73">
-        <v>-8.941301922840431</v>
+        <v>-10.18186832029371</v>
       </c>
       <c r="F73">
-        <v>4.671704561052932</v>
+        <v>5.159450601290892</v>
       </c>
       <c r="G73">
-        <v>-1.035827812814278</v>
+        <v>-0.5513725102339501</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.025917702039198</v>
       </c>
       <c r="E74">
-        <v>-9.428597425383815</v>
+        <v>-9.24753997760914</v>
       </c>
       <c r="F74">
-        <v>4.399443390040013</v>
+        <v>4.865499458203071</v>
       </c>
       <c r="G74">
-        <v>-0.377949582159229</v>
+        <v>-0.1325289096964381</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.97256345131316</v>
       </c>
       <c r="E75">
-        <v>-9.009351301753695</v>
+        <v>-10.41257595708849</v>
       </c>
       <c r="F75">
-        <v>4.389378726095999</v>
+        <v>5.255252948159461</v>
       </c>
       <c r="G75">
-        <v>-0.4080093356558114</v>
+        <v>0.3742791963650487</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.881023538148837</v>
       </c>
       <c r="E76">
-        <v>-8.642735103040717</v>
+        <v>-10.08609109503148</v>
       </c>
       <c r="F76">
-        <v>4.421232766203252</v>
+        <v>4.970934061231392</v>
       </c>
       <c r="G76">
-        <v>-0.2220890981703415</v>
+        <v>0.6088247267313337</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.754295024339841</v>
       </c>
       <c r="E77">
-        <v>-10.41828183433815</v>
+        <v>-11.24243693289011</v>
       </c>
       <c r="F77">
-        <v>4.109239781082457</v>
+        <v>4.88366721208127</v>
       </c>
       <c r="G77">
-        <v>-0.3207036286941516</v>
+        <v>1.181032659921123</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.597815337098493</v>
       </c>
       <c r="E78">
-        <v>-11.36518574934202</v>
+        <v>-10.95446221379433</v>
       </c>
       <c r="F78">
-        <v>3.374298967440291</v>
+        <v>4.586173969979078</v>
       </c>
       <c r="G78">
-        <v>0.6519809983812729</v>
+        <v>0.7871439516586369</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.417343255458089</v>
       </c>
       <c r="E79">
-        <v>-9.506695488120098</v>
+        <v>-10.45436924370527</v>
       </c>
       <c r="F79">
-        <v>3.996333304080884</v>
+        <v>4.558234794217456</v>
       </c>
       <c r="G79">
-        <v>0.2601183439888211</v>
+        <v>0.9611826412036625</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.216775733125348</v>
       </c>
       <c r="E80">
-        <v>-13.67937634995581</v>
+        <v>-10.97225911664448</v>
       </c>
       <c r="F80">
-        <v>3.829679036516068</v>
+        <v>4.436998254613332</v>
       </c>
       <c r="G80">
-        <v>-1.049566576802253</v>
+        <v>0.3617388498622894</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.004191396703794</v>
       </c>
       <c r="E81">
-        <v>-12.71266488964239</v>
+        <v>-13.57019937010489</v>
       </c>
       <c r="F81">
-        <v>3.369918560614287</v>
+        <v>4.701431353669795</v>
       </c>
       <c r="G81">
-        <v>0.2248444812678866</v>
+        <v>1.990441180999692</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.788166697616651</v>
       </c>
       <c r="E82">
-        <v>-12.46437771674984</v>
+        <v>-13.25967737892492</v>
       </c>
       <c r="F82">
-        <v>4.082087554353495</v>
+        <v>4.423174459395414</v>
       </c>
       <c r="G82">
-        <v>0.613039051202826</v>
+        <v>1.268580036707149</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.576651239903152</v>
       </c>
       <c r="E83">
-        <v>-13.95823525087414</v>
+        <v>-14.9255580551786</v>
       </c>
       <c r="F83">
-        <v>3.401134757821384</v>
+        <v>4.592732983074445</v>
       </c>
       <c r="G83">
-        <v>1.499152912426309</v>
+        <v>2.908607744134399</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.373815192229413</v>
       </c>
       <c r="E84">
-        <v>-15.77441145096839</v>
+        <v>-14.45125927303723</v>
       </c>
       <c r="F84">
-        <v>3.922903504027125</v>
+        <v>4.36667151885046</v>
       </c>
       <c r="G84">
-        <v>1.504304121285415</v>
+        <v>1.892753603226878</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.184790565228652</v>
       </c>
       <c r="E85">
-        <v>-15.04966088535881</v>
+        <v>-16.39092243084664</v>
       </c>
       <c r="F85">
-        <v>3.575539230806791</v>
+        <v>4.13270245939935</v>
       </c>
       <c r="G85">
-        <v>0.3022351043394291</v>
+        <v>2.093574606184608</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.014584417377032</v>
       </c>
       <c r="E86">
-        <v>-16.90199695040431</v>
+        <v>-18.06949189126982</v>
       </c>
       <c r="F86">
-        <v>3.251384155478095</v>
+        <v>4.323672623705942</v>
       </c>
       <c r="G86">
-        <v>0.2635282058942704</v>
+        <v>2.089558914445472</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.867110840819552</v>
       </c>
       <c r="E87">
-        <v>-20.96657860920292</v>
+        <v>-18.40697188821744</v>
       </c>
       <c r="F87">
-        <v>3.045160433816352</v>
+        <v>4.306830257672223</v>
       </c>
       <c r="G87">
-        <v>2.484487134007289</v>
+        <v>2.975937619312096</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.74255845447701</v>
       </c>
       <c r="E88">
-        <v>-19.84368460883896</v>
+        <v>-20.91488154993135</v>
       </c>
       <c r="F88">
-        <v>2.945446536071764</v>
+        <v>4.376729555855251</v>
       </c>
       <c r="G88">
-        <v>0.9672343184494503</v>
+        <v>3.587378827687788</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.639928879475169</v>
       </c>
       <c r="E89">
-        <v>-21.79408025004655</v>
+        <v>-22.03282592820494</v>
       </c>
       <c r="F89">
-        <v>3.37269193467886</v>
+        <v>3.742925775155682</v>
       </c>
       <c r="G89">
-        <v>1.810489857121528</v>
+        <v>2.723442311031883</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.559496432336641</v>
       </c>
       <c r="E90">
-        <v>-23.67417586075906</v>
+        <v>-23.77687259430501</v>
       </c>
       <c r="F90">
-        <v>2.759608936192917</v>
+        <v>3.729758046920781</v>
       </c>
       <c r="G90">
-        <v>1.914073516499785</v>
+        <v>3.350539089262788</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.501561669007585</v>
       </c>
       <c r="E91">
-        <v>-22.99196577997753</v>
+        <v>-23.64084629206261</v>
       </c>
       <c r="F91">
-        <v>2.808958095847295</v>
+        <v>3.574238693984396</v>
       </c>
       <c r="G91">
-        <v>2.421404688756476</v>
+        <v>3.161129536778926</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.463873262925162</v>
       </c>
       <c r="E92">
-        <v>-26.29866655732644</v>
+        <v>-26.78665038791899</v>
       </c>
       <c r="F92">
-        <v>2.344514030650085</v>
+        <v>2.925106802863426</v>
       </c>
       <c r="G92">
-        <v>1.961000499518954</v>
+        <v>2.208645858584135</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.441798947843214</v>
       </c>
       <c r="E93">
-        <v>-27.71554456179436</v>
+        <v>-28.48149065545173</v>
       </c>
       <c r="F93">
-        <v>2.86836694924127</v>
+        <v>2.762847852737864</v>
       </c>
       <c r="G93">
-        <v>2.032859200994374</v>
+        <v>2.614157892235002</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.433640286105794</v>
       </c>
       <c r="E94">
-        <v>-30.20159980794726</v>
+        <v>-30.33309310770798</v>
       </c>
       <c r="F94">
-        <v>2.066972845811722</v>
+        <v>3.214596359119768</v>
       </c>
       <c r="G94">
-        <v>1.461803337652251</v>
+        <v>3.118708206238705</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.438984419658463</v>
       </c>
       <c r="E95">
-        <v>-31.86836353663243</v>
+        <v>-31.55951708083531</v>
       </c>
       <c r="F95">
-        <v>2.041310023672994</v>
+        <v>2.816080398776565</v>
       </c>
       <c r="G95">
-        <v>0.9327351233847052</v>
+        <v>2.068335006993204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.453991857435345</v>
       </c>
       <c r="E96">
-        <v>-34.6615240403265</v>
+        <v>-33.7232219617002</v>
       </c>
       <c r="F96">
-        <v>1.696502092257699</v>
+        <v>2.274893063914398</v>
       </c>
       <c r="G96">
-        <v>1.520340403877644</v>
+        <v>2.898815150429235</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.473015009699861</v>
       </c>
       <c r="E97">
-        <v>-37.51100517525397</v>
+        <v>-35.77840422720828</v>
       </c>
       <c r="F97">
-        <v>1.694972926032131</v>
+        <v>1.847583052649884</v>
       </c>
       <c r="G97">
-        <v>1.399379690963754</v>
+        <v>2.78873289015739</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.490654350314245</v>
       </c>
       <c r="E98">
-        <v>-39.086169195949</v>
+        <v>-38.01785236432547</v>
       </c>
       <c r="F98">
-        <v>1.782506509485955</v>
+        <v>2.092198289961773</v>
       </c>
       <c r="G98">
-        <v>0.8197296514016833</v>
+        <v>1.967181288040773</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.503799085918907</v>
       </c>
       <c r="E99">
-        <v>-40.67944258420069</v>
+        <v>-40.81584927825974</v>
       </c>
       <c r="F99">
-        <v>1.000164856320796</v>
+        <v>1.679194183743606</v>
       </c>
       <c r="G99">
-        <v>1.535052468254166</v>
+        <v>2.618643681440714</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.504189897612195</v>
       </c>
       <c r="E100">
-        <v>-43.65582967471912</v>
+        <v>-43.14693108692214</v>
       </c>
       <c r="F100">
-        <v>1.289051361107901</v>
+        <v>1.223747845275605</v>
       </c>
       <c r="G100">
-        <v>0.1174536945194685</v>
+        <v>2.363943549831346</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.487834514178247</v>
       </c>
       <c r="E101">
-        <v>-44.92930222854913</v>
+        <v>-46.11700095619986</v>
       </c>
       <c r="F101">
-        <v>0.8415109611322176</v>
+        <v>1.146613586196526</v>
       </c>
       <c r="G101">
-        <v>0.9660425220553126</v>
+        <v>1.680243063969982</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.44220818649318</v>
       </c>
       <c r="E102">
-        <v>-47.92383265017929</v>
+        <v>-47.44795343060924</v>
       </c>
       <c r="F102">
-        <v>0.5150165762580149</v>
+        <v>0.9425452765168677</v>
       </c>
       <c r="G102">
-        <v>1.388375437591217</v>
+        <v>1.193149256594855</v>
       </c>
     </row>
   </sheetData>
